--- a/Data/Skyways_Timeline_Data.xlsx
+++ b/Data/Skyways_Timeline_Data.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.43" customWidth="1" style="13" min="1" max="1"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Skyways raised its seed round on a rolling basis over the first several years of the company, bringing in capital as needed rather than in a single close. Investors included Capital Factory, Social Capital, UpHonest Capital, NextView Ventures, Outlander VC, MVP Ventures, and others. Total private equity raised remained modest relative to peers.</t>
+          <t>Skyways raised its seed round on a rolling basis over the first several years of the company, bringing in capital as needed rather than in a single close. Early investors included Capital Factory, Social Capital, Liquid 2 Ventures, NextView Ventures, Pi Campus, Graph Ventures, and others. Total private equity raised remained modest relative to peers.</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>Crunchbase — Funding Rounds (Fact Error: Showed single $1M round with close date; was actually a rolling close over multiple years)</t>
+          <t>Crunchbase — Funding Rounds (Fact Error: Showed single $1M round with close date; was actually a rolling close over multiple years. May still list UpHonest Capital, which has been removed from cap table)</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Charles Acknin Source Correction — Seed round was a rolling close over multiple years, not a single round; see linked spreadsheet</t>
+          <t>Charles Acknin Source Correction — Seed round was a rolling close over multiple years, not a single round. Outlander VC and MVP Ventures were 2021+ investors, not seed. UpHonest Capital removed from cap table. See investor spreadsheet for full details</t>
         </is>
       </c>
       <c r="J6" s="17" t="n"/>
@@ -1233,12 +1233,12 @@
     <row r="12">
       <c r="A12" s="33" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>~2020</t>
+          <t>End of 2017</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t>The U.S. Marine Corps, in partnership with the Georgia Institute of Technology / Georgia Tech Research Institute (GTRI), issued Skyways' very first purchase order — for two V2.2 aircraft. This represented Skyways' first hardware sale and a critical early validation of the platform's readiness for military customers beyond the Navy's Blue Water program. No published press coverage found; milestone confirmed by CEO Charles Acknin.</t>
+          <t>The U.S. Marine Corps, in partnership with the Georgia Institute of Technology / Georgia Tech Research Institute (GTRI), issued Skyways' very first purchase order — for two V2.2 aircraft. This represented Skyways' first hardware sale and a critical early validation of the platform's readiness for military customers. No published press coverage found; milestone confirmed by CEO Charles Acknin.</t>
         </is>
       </c>
       <c r="F12" s="33" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" s="36" t="inlineStr">
         <is>
-          <t>Charles Acknin Source Correction — USMC/GTRI was Skyways' very first PO for two V2.2 aircraft. Purchase order issued by USMC in partnership with Georgia Institute of Technology / GTRI. Internal contract docs at: https://drive.google.com/drive/folders/1t-le78CkMLCC9CyVO-ocg1M5W8QdYL2W</t>
+          <t>Charles Acknin Source Correction — USMC/GTRI PO was end of 2017 (not ~2020), Skyways' very first contract/PO. Purchase order issued by USMC in partnership with Georgia Institute of Technology / GTRI. Internal contract docs at: https://drive.google.com/drive/folders/1t-le78CkMLCC9CyVO-ocg1M5W8QdYL2W</t>
         </is>
       </c>
       <c r="I12" s="36" t="n"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>The original August 2019 Navy OTA ($575,141) expanded through multiple spiral development follow-on contracts, growing to approximately four times its original value (~$2.3M). These follow-on awards funded progressive capability demonstrations including the transition to hybrid propulsion, folding wings development, and increasingly complex ship-based operations.</t>
+          <t>The original August 2019 Navy OTA ($575,141) funded the transition from all-electric to hybrid propulsion. Subsequent spiral development follow-on contracts grew the total to approximately four times the original value (~$2.3M), funding folding wings development and increasingly complex ship-based operations.</t>
         </is>
       </c>
       <c r="F13" s="33" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>Charles Acknin Source Correction — Multiple spiral development follow-on OTA contracts with USN. Contract docs at: https://drive.google.com/drive/folders/1zttPYwgd9uVGe_uzxiQnW1FcY-EeJLj9</t>
+          <t>Charles Acknin Source Correction — First contract was for hybrid propulsion, then spiral dev added folding wings and ship ops. Contract docs at: https://drive.google.com/drive/folders/1zttPYwgd9uVGe_uzxiQnW1FcY-EeJLj9</t>
         </is>
       </c>
       <c r="J13" s="19" t="n"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Continuous refinement through sub-variants (V2.2, V2.5, V2.6, V2.6b). SkyNav autonomous software matures — coordinates multi-aircraft operations and integrates with third-party UTM systems. Flight testing near Giddings, TX. Starlink connectivity later added, which Acknin says transformed operations from 'the AOL days.'</t>
+          <t>Continuous refinement through sub-variants (V2.2, V2.5, V2.6, V2.6b). Flight testing near Giddings, TX. SkyNav autonomous software (developed starting Q2 2023) would later coordinate multi-aircraft operations and integrate with third-party UTM systems. Starlink connectivity (added end of 2024) transformed operations from 'the AOL days,' per Acknin.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1387,7 +1387,11 @@
           <t>SBIR.gov — V2.5 referenced</t>
         </is>
       </c>
-      <c r="I14" s="8" t="n"/>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — SkyNav started Q2 2023 (not 2020); Starlink connectivity started end of 2024 (not 2020)</t>
+        </is>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="Q14" s="30" t="inlineStr">
@@ -1483,7 +1487,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Air Force SBIR topic AF203-CSO1. This $47,775 Phase I award began the AFWERX SBIR pathway that would lead to $37M. The SBIR program provides a structured pathway from small exploratory awards to large-scale production contracts through progressive phases.</t>
+          <t>Air Force SBIR topic AF203-CSO1. This $47,775 Phase I award began the AFWERX SBIR pathway that would eventually lead to the USAF awarding Skyways a $37M contract. The SBIR program provides a structured pathway from small exploratory awards to large-scale production contracts through progressive phases.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1512,697 +1516,743 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2021</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>First Commercial Customer — Offshore Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Revenue-generating offshore platform resupply begins with unnamed oil-and-gas customer. First non-defense customer, validating the dual-use thesis of the platform. Revenue reportedly doubled for three consecutive years through January 2026.</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Contract — Commercial</t>
-        </is>
-      </c>
-      <c r="G17" s="37" t="inlineStr">
-        <is>
-          <t>SBIR.gov — Phase I references O&amp;G</t>
-        </is>
-      </c>
-      <c r="H17" s="37" t="inlineStr">
-        <is>
-          <t>The Drone Girl — Inside Skyways</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="Q17" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R17" s="28" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Jul 2021</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Ship-to-Ship Autonomous Flights</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Defense Milestones</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>V2 flies between USS Bainbridge (DDG-96) and USNS Joshua Humphreys (T-AO-188). These flights were conducted entirely by U.S. Navy personnel — no Skyways employees were on either ship, a significant achievement demonstrating the system's operational maturity and ease of use by military operators.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>USNI News — Navy Considering Drone Delivery (Aug 2021)</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — All flights conducted by U.S. Navy personnel only; no Skyways employees on ships. Computer vision was only used for final VTOL landing (precland) at this time; full Computer Vision Ship Intercept (CVSI) was not achieved until Nov 2024</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="20" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="Q17" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R17" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2021</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Ship-to-Ship Autonomous Flights</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Defense Milestones</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>V2 flies between USS Bainbridge (DDG-96) and USNS Joshua Humphreys (T-AO-188). These flights were conducted entirely by U.S. Navy personnel — no Skyways employees were on either ship, a significant achievement demonstrating the system's operational maturity and ease of use by military operators. The drone autonomously navigated to the moving ship using only rough coordinates, identifying and intercepting the vessel through computer vision.</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="G18" s="40" t="inlineStr">
-        <is>
-          <t>USNI News — Navy Considering Drone Delivery (Aug 2021)</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — All flights conducted by U.S. Navy personnel only; no Skyways employees on ships</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="Q18" s="31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R18" s="31" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2021</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Moved Into Austin Cross Park Drive — 10,000 SF</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Major Milestones</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Facility expansion to 10,000 SF on Cross Park Drive in Austin to support Navy contract execution and growing aircraft fleet. This replaced the Manor office as the company scaled operations for Blue Water program deliverables.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Skyways Internal — Not Published</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Cross Park Dr move was Apr 2021 (not May 2021)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="Q18" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R18" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Apr 2021</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Moved Into Austin Cross Park Drive — 10,000 SF</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Major Milestones</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Facility expansion to 10,000 SF on Cross Park Drive in Austin to support Navy contract execution and growing aircraft fleet. This replaced the Manor office as the company scaled operations for Blue Water program deliverables.</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Skyways Internal — Not Published</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Cross Park Dr move was Apr 2021 (not May 2021)</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="Q19" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R19" s="26" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Jul 2022</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>SBIR Phase II — $749,711</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Contracts &amp; Funding</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>AFWERX SBIR pathway continues with $749,711 Phase II under topic AF203-CSO1. Funds continued V2 development and autonomous systems advancement. A 15× increase from Phase I, reflecting the Air Force's growing confidence in Skyways' technology.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Contract — U.S. Air Force</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>SBIR.gov — Skyways Portfolio</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Phase II was for V2 work, not V3; removed V3 reference</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="Q19" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R19" s="28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Jul 2022</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>SBIR Phase II — $749,711</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>AFWERX SBIR pathway continues with $749,711 Phase II under topic AF203-CSO1. Funds continued V2 development and autonomous systems advancement. A 15× increase from Phase I, reflecting the Air Force's growing confidence in Skyways' technology.</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Contract — U.S. Air Force</t>
-        </is>
-      </c>
-      <c r="G20" s="37" t="inlineStr">
-        <is>
-          <t>SBIR.gov — Skyways Portfolio</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Phase II was for V2 work, not V3; removed V3 reference</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="Q20" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R20" s="28" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Dec 2022</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>200+ NM Cargo Delivery Demonstrations</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Defense Milestones</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Multi-mode operations at NAS Patuxent River: ship-to-ship, ship-to-shore, shore-to-ship across 200+ nautical miles. Navy publicly confirmed unmanned cargo delivery at sea through official NAVAIR press release, providing critical public validation of autonomous maritime logistics viability.</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>NAVAIR — Navy Demonstrates Unmanned Cargo Delivery (Dec 2022)</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="inlineStr">
+        <is>
+          <t>USNI News — Navy to Deploy Four Cargo Drones on Carrier (Apr 2022)</t>
+        </is>
+      </c>
+      <c r="I20" s="40" t="inlineStr">
+        <is>
+          <t>DroneXL — Navy Drone Delivery Trials (Jan 2023)</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="Q20" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R20" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Dec 2022</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>200+ NM Cargo Delivery Demonstrations</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Defense Milestones</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Multi-mode operations at NAS Patuxent River: ship-to-ship, ship-to-shore, shore-to-ship across 200+ nautical miles. Navy publicly confirmed unmanned cargo delivery at sea through official NAVAIR press release, providing critical public validation of autonomous maritime logistics viability.</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="G21" s="40" t="inlineStr">
-        <is>
-          <t>NAVAIR — Navy Demonstrates Unmanned Cargo Delivery (Dec 2022)</t>
-        </is>
-      </c>
-      <c r="H21" s="40" t="inlineStr">
-        <is>
-          <t>USNI News — Navy to Deploy Four Cargo Drones on Carrier (Apr 2022)</t>
-        </is>
-      </c>
-      <c r="I21" s="40" t="inlineStr">
-        <is>
-          <t>DroneXL — Navy Drone Delivery Trials (Jan 2023)</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="Q21" s="31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R21" s="31" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>DIU/USN/NAMD Contract</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Contracts &amp; Funding</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Skyways secured a contract through the Defense Innovation Unit (DIU) in partnership with the U.S. Navy and NAMD. The award contract was directly issued by Army Contracting Command – New Jersey (ACC-NJ). Specific scope and value not publicly disclosed. No published press coverage found; milestone confirmed by CEO Charles Acknin.</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Contract — DIU / U.S. Navy</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>Skyways Internal - No Source</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — DIU contract/OTA won in 2022 (not ~2023). Award issued by Army Contracting Command NJ (ACC-NJ). Follow-on contracts earned on same OTA. Internal docs at: https://drive.google.com/drive/folders/1crUdAexYQCpU2RPWEx5tMxzqgovXdIkD</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="Q21" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R21" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="13">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>~2023</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>~2023</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>DIU/USN/NAMD Contract</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>Skyways secured a contract through the Defense Innovation Unit (DIU) in partnership with the U.S. Navy and NAMD. The award contract was directly issued by Army Contracting Command – New Jersey (ACC-NJ). Specific scope and value not publicly disclosed. No published press coverage found; milestone confirmed by CEO Charles Acknin.</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Contract — DIU / U.S. Navy</t>
-        </is>
-      </c>
-      <c r="G22" s="36" t="inlineStr">
-        <is>
-          <t>Skyways Internal - No Source</t>
-        </is>
-      </c>
-      <c r="H22" s="36" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — DIU/USN/NAMD contract exists. Award issued by Army Contracting Command NJ (ACC-NJ). No published source found; internal contract docs at: https://drive.google.com/drive/folders/1crUdAexYQCpU2RPWEx5tMxzqgovXdIkD</t>
-        </is>
-      </c>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="Q22" s="35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R22" s="35" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Jun 2023</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Fleet Battle Problem 23-1 — First Logistics Drone in a Fleet Exercise</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Defense Milestones</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Autonomous flights from USNS Patuxent to Marines at Camp Lejeune, NC during FBP 23-1 (June 9–13). First logistics drone integrated into a U.S. fleet exercise. Five flights completed, demonstrating ship-to-shore resupply in a realistic military exercise with Navy and USMC. NAWCAD partnered with Military Sealift Command and USMC.</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Defense — U.S. Navy / USMC</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>DVIDS — NAWCAD Teams with MSC, Marines (Jun 2023)</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="inlineStr">
+        <is>
+          <t>MSC/Navy.mil — NAWCAD Teams with MSC, Marines (Jun 2023)</t>
+        </is>
+      </c>
+      <c r="I22" s="40" t="inlineStr">
+        <is>
+          <t>Inside Unmanned Systems — Navy Drone Delivery at Sea</t>
+        </is>
+      </c>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>Navy.mil — Fleet Battle Problem 23-1</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="10" t="n"/>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R22" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="13">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Jun 2023</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Fleet Battle Problem 23-1 — First Logistics Drone in a Fleet Exercise</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Defense Milestones</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Autonomous flights from USNS Patuxent to Marines at Camp Lejeune, NC during FBP 23-1 (June 9–13). First logistics drone integrated into a U.S. fleet exercise. Five flights completed, demonstrating ship-to-shore resupply in a realistic military exercise with Navy and USMC. NAWCAD partnered with Military Sealift Command and USMC.</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Defense — U.S. Navy / USMC</t>
-        </is>
-      </c>
-      <c r="G23" s="40" t="inlineStr">
-        <is>
-          <t>DVIDS — NAWCAD Teams with MSC, Marines (Jun 2023)</t>
-        </is>
-      </c>
-      <c r="H23" s="40" t="inlineStr">
-        <is>
-          <t>MSC/Navy.mil — NAWCAD Teams with MSC, Marines (Jun 2023)</t>
-        </is>
-      </c>
-      <c r="I23" s="40" t="inlineStr">
-        <is>
-          <t>Inside Unmanned Systems — Navy Drone Delivery at Sea</t>
-        </is>
-      </c>
-      <c r="J23" s="38" t="inlineStr">
-        <is>
-          <t>Navy.mil — Fleet Battle Problem 23-1</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="10" t="n"/>
-      <c r="Q23" s="31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R23" s="31" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>V3 Next-Generation Platform Revealed</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Product Development</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>V3 specs: 100-lb payload (5 ft³), 1,000+ mi range, 20+ hr endurance — ~3× V2 capability. Wingspan ~26 ft, heavy-fuel engine + pusher propeller. SBIR designation 'SKYWAYS V3 300LB VTOL UAS' suggests 300-lb gross weight. V3 development timeline: initial concept (2021), subscale with test flights (Oct 2022), Block 0 full-scale first flew (early 2023), Block 1 full-scale first flew (early 2024), Block 2 first article build (scheduled Jun 2026). Significant resources dedicated from mid-2023 onward. Progresses through Block designations (0 → 1 → 2 → 2+).</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G23" s="39" t="inlineStr">
+        <is>
+          <t>sUAS News — Skyways V3</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — V3 timeline: concept 2021, subscale 2022, Block 0 flew early 2023, Block 1 flew early 2024, Block 2 first article Jun 2026. Major investment from mid-2023</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="Q23" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R23" s="30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="13">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>V3 Next-Generation Platform Revealed</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Product Development</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>V3 specs: 100-lb payload (5 ft³), 1,000+ mi range, 20+ hr endurance — ~3× V2 capability. Wingspan ~26 ft, heavy-fuel engine + pusher propeller. SBIR designation 'SKYWAYS V3 300LB VTOL UAS' suggests 300-lb gross weight. Described as 'technically the seventh generation aircraft' after dozens of iterations. Progresses through Block designations (0 → 1 → 2 → 2+).</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G24" s="39" t="inlineStr">
-        <is>
-          <t>sUAS News — Skyways V3</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="Q24" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R24" s="30" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>RIMPAC 2024 — USS Curtis Wilbur (DDG-54)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Defense Milestones</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Three Skyways V2.6 aircraft launched and recovered from USS Curtis Wilbur (DDG-54) alongside PteroDynamics X-P4 drones during Trident Warrior at RIMPAC 2024, the world's largest international maritime exercise. Simulated Just-In-Time Delivery of medical supplies and critical parts. Demonstrated capability in a multinational exercise environment.</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>Defense News — Navy tests drones for medical supply at RIMPAC (Jul 2024) (Note: 'six drones' count includes both Skyways and PteroDynamics aircraft)</t>
+        </is>
+      </c>
+      <c r="H24" s="40" t="inlineStr">
+        <is>
+          <t>The Aviationist — U.S. Navy Tests VTOL Drones for Cargo (Jul 2024)</t>
+        </is>
+      </c>
+      <c r="I24" s="40" t="inlineStr">
+        <is>
+          <t>Eurasian Times — US Navy Demonstrates Unmanned Cargo Delivery</t>
+        </is>
+      </c>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>SURFPAC/Navy.mil — USS Curtis Wilbur Tests Drones During RIMPAC Trident Warrior 2024</t>
+        </is>
+      </c>
+      <c r="K24" s="40" t="inlineStr">
+        <is>
+          <t>Battle Updates — Unmanned Systems Update</t>
+        </is>
+      </c>
+      <c r="L24" s="40" t="inlineStr">
+        <is>
+          <t>DVIDS — USS Curtis Wilbur Tests Drones During RIMPAC Trident Warrior 2024</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Three Skyways aircraft on that DDG (not six); six total included PteroDynamics X-P4 drones</t>
+        </is>
+      </c>
+      <c r="Q24" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R24" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="13">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Jun 2024</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>RIMPAC 2024 — USS Curtis Wilbur (DDG-54)</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>III MEF — Temperature Controlled Payload (TCP) Demonstration</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>Defense Milestones</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>Six UAS launched and recovered from USS Curtis Wilbur (DDG-54) during Trident Warrior at RIMPAC 2024, the world's largest international maritime exercise. Simulated Just-In-Time Delivery of medical supplies and critical parts. Demonstrated capability in a multinational exercise environment.</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="G25" s="40" t="inlineStr">
-        <is>
-          <t>Defense News — Navy tests drones for medical supply at RIMPAC (Jul 2024)</t>
-        </is>
-      </c>
-      <c r="H25" s="40" t="inlineStr">
-        <is>
-          <t>The Aviationist — U.S. Navy Tests VTOL Drones for Cargo (Jul 2024)</t>
-        </is>
-      </c>
-      <c r="I25" s="40" t="inlineStr">
-        <is>
-          <t>Eurasian Times — US Navy Demonstrates Unmanned Cargo Delivery</t>
-        </is>
-      </c>
-      <c r="J25" s="38" t="inlineStr">
-        <is>
-          <t>SURFPAC/Navy.mil — USS Curtis Wilbur Tests Drones During RIMPAC Trident Warrior 2024</t>
-        </is>
-      </c>
-      <c r="K25" s="40" t="inlineStr">
-        <is>
-          <t>Battle Updates — Unmanned Systems Update</t>
-        </is>
-      </c>
-      <c r="L25" s="40" t="inlineStr">
-        <is>
-          <t>DVIDS — USS Curtis Wilbur Tests Drones During RIMPAC Trident Warrior 2024</t>
-        </is>
-      </c>
-      <c r="Q25" s="31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R25" s="31" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Under a DIU contract modification, Skyways demonstrated Temperature Controlled Payload (TCP) capability with USMC III MEF. Operations were conducted in the US (not overseas). Skyways completed a 6-hour flight covering over 300 miles while keeping 10 bags of blood cool at 3–6°C throughout the entire flight. No published press coverage found; milestone confirmed by CEO Charles Acknin.</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Defense — USMC / III MEF</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>Skyways Internal - No Source</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — III MEF TCP demo was a DIU contract mod, conducted in the US (not Japan). 6h flight, 300+ miles, 10 bags of blood at 3–6°C. Internal docs at: https://drive.google.com/drive/folders/1ShFq3aQydYzACrFfLZ0LKbPYyLaG7mYb and https://drive.google.com/drive/folders/116oBSkyQrcOM1LrVpVEMTboFzdi9tqZ2</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="Q25" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R25" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="13">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>~2024–2025</t>
-        </is>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>~2024–2025</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>III Marine Expeditionary Force (III MEF) Operations</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>Defense Milestones</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Skyways conducted operations or demonstrations with III Marine Expeditionary Force (III MEF), the U.S. Marine Corps command based in Okinawa, Japan responsible for Marine operations across the Indo-Pacific. Details of scope and specific demonstrations not publicly disclosed.</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Defense — USMC / III MEF</t>
-        </is>
-      </c>
-      <c r="G26" s="36" t="inlineStr">
-        <is>
-          <t>Skyways Internal - No Source</t>
-        </is>
-      </c>
-      <c r="H26" s="36" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — III MEF work confirmed. No published source found; internal docs at: https://drive.google.com/drive/folders/1ShFq3aQydYzACrFfLZ0LKbPYyLaG7mYb and https://drive.google.com/drive/folders/116oBSkyQrcOM1LrVpVEMTboFzdi9tqZ2</t>
-        </is>
-      </c>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n"/>
-      <c r="Q26" s="35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R26" s="35" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>USAF SBIR Phase 3 IDIQ Contract &amp; STRATFI Selection</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Contracts &amp; Funding</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>After submitting the STRATFI package in approximately September 2023, USAF AFWERX issued an RFP to Skyways in early 2024 to begin V3 development. In June 2024, Skyways was awarded a SBIR Phase 3 IDIQ contract to start turning V3 into a product. In the same month, Skyways received notification it had been selected for STRATFI funding, which would ultimately be awarded as the $37M contract in May 2025.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Contract — U.S. Air Force</t>
+        </is>
+      </c>
+      <c r="G26" s="37" t="inlineStr">
+        <is>
+          <t>SBIR.gov — Skyways Portfolio (Fact Error: Listed $3.55M STRATFI amount; Charles says figure is wrong and timeline differs)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — $3.55M figure was wrong; corrected STRATFI timeline: Sep 2023 submit → Feb 2024 RFP → Jun 2024 Phase 3 IDIQ + selection → May 2025 $37M award</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="Q26" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R26" s="28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="13">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2024</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>USAF SBIR Phase 3 IDIQ Contract &amp; STRATFI Selection</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>After submitting the STRATFI package in approximately September 2023, USAF AFWERX issued an RFP to Skyways in early 2024 to begin V3 development. In June 2024, Skyways was awarded a SBIR Phase 3 IDIQ contract (initial millions) to start turning V3 into a product. In the same month, Skyways received notification it had been selected for STRATFI funding, which would ultimately be awarded as the $37M contract in May 2025.</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Contract — U.S. Air Force</t>
-        </is>
-      </c>
-      <c r="G27" s="37" t="inlineStr">
-        <is>
-          <t>SBIR.gov — Skyways Portfolio (Fact Error: Listed $3.55M STRATFI amount; Charles says figure is wrong and timeline differs)</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — $3.55M figure was wrong; corrected STRATFI timeline: Sep 2023 submit → Feb 2024 RFP → Jun 2024 Phase 3 IDIQ + selection → May 2025 $37M award</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="Q27" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R27" s="28" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>May 2024</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Moved into Austin Tech Ridge — 25,000 SF</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Major Milestones</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>New 25,000 SF facility at Tech Ridge in North Austin provides manufacturing space needed for V3 production ramp and growing headcount. This facility remains the current headquarters as of 2026.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Skyways Internal — Not Published</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Tech Ridge move was May 2024 (not May 2025)</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="Q27" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R27" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="13">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>May 2024</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Moved into Austin Tech Ridge — 25,000 SF</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Major Milestones</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>New 25,000 SF facility at Tech Ridge in North Austin provides manufacturing space needed for V3 production ramp and growing headcount. This facility remains the current headquarters as of 2026.</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Skyways Internal — Not Published</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Tech Ridge move was May 2024 (not May 2025)</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="Q28" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R28" s="26" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>$37M U.S. Air Force STRATFI Contract</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Contracts &amp; Funding</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>One of the largest AFWERX STRATFI awards ever given to an autonomous drone company and the only STRATFI in the cargo drone industry. STRATFI is a critical pathway to a Program of Record (PoR) — a formal DoD-recognized acquisition program that unlocks large-scale, sustained procurement. Funds V3 transition from prototype to full-rate production. Validates the SBIR pathway from $47K Phase I to $37M STRATFI over four years.</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Contract — U.S. Air Force</t>
+        </is>
+      </c>
+      <c r="G28" s="37" t="inlineStr">
+        <is>
+          <t>DC Velocity — Texas firm gains $37M Air Force backing</t>
+        </is>
+      </c>
+      <c r="H28" s="37" t="inlineStr">
+        <is>
+          <t>The Defense Post — Skyways Lands $37M USAF Deal (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="I28" s="37" t="inlineStr">
+        <is>
+          <t>Austin Business Journal — Defense-tech startup wins contract</t>
+        </is>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Total contract value is $37M, not $41M; award date is May 2025</t>
+        </is>
+      </c>
+      <c r="K28" s="37" t="inlineStr">
+        <is>
+          <t>Business Wire — Press Release (Fact Error: Listed June 2025 and implied $41M total contract value; actual award was May 2025 and total is $37M)</t>
+        </is>
+      </c>
+      <c r="L28" s="37" t="inlineStr">
+        <is>
+          <t>DroneLife — Skyways Lands $37M Contract (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="M28" s="38" t="inlineStr">
+        <is>
+          <t>AP News — Skyways Secures $37M USAF Contract (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="N28" s="38" t="inlineStr">
+        <is>
+          <t>The Drone Girl — Skyways V3 Autonomous Cargo Drone (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="O28" s="38" t="inlineStr">
+        <is>
+          <t>UAS Weekly — Skyways Wins $37M USAF Contract (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="P28" s="38" t="inlineStr">
+        <is>
+          <t>Yahoo Finance — Skyways Secures $37M Contract (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="Q28" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R28" s="28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2216,12 +2266,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>May 2025</t>
+          <t>Jun 2025</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>$37M U.S. Air Force STRATFI Contract</t>
+          <t>$7M Equity Raise + $5M Leonid Debt Facility</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2231,67 +2281,39 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>One of the largest AFWERX STRATFI awards ever given to an autonomous drone company. Funds V3 transition from prototype to full-rate production and positions for Program of Record designation, unlocking large-scale DoD procurement. Validates the SBIR pathway from $47K Phase I to $37M STRATFI over four years.</t>
+          <t>Skyways raised $7M in private equity to provide initial private funding for the STRATFI 1:1:2 Government:SBIR:Private matching structure required for the $37M contract. Separately, Skyways secured a $5M debt facility from defense-specialist lender Leonid Capital Partners for cashflow management during production ramp.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Contract — U.S. Air Force</t>
+          <t>Funding</t>
         </is>
       </c>
       <c r="G29" s="37" t="inlineStr">
         <is>
-          <t>DC Velocity — Texas firm gains $37M Air Force backing</t>
+          <t>Business Wire — $5M Debt Facility Announcement</t>
         </is>
       </c>
       <c r="H29" s="37" t="inlineStr">
         <is>
-          <t>The Defense Post — Skyways Lands $37M USAF Deal (Jun 2025)</t>
+          <t>DroneLife — Skyways Secures $5M for Production (Jul 2025)</t>
         </is>
       </c>
       <c r="I29" s="37" t="inlineStr">
         <is>
-          <t>Austin Business Journal — Defense-tech startup wins contract</t>
+          <t>Skyways Newsroom</t>
         </is>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>Charles Acknin Source Correction — Total contract value is $37M, not $41M; award date is May 2025</t>
-        </is>
-      </c>
-      <c r="K29" s="37" t="inlineStr">
-        <is>
-          <t>Business Wire — Press Release (Fact Error: Listed June 2025 and implied $41M total contract value; actual award was May 2025 and total is $37M)</t>
-        </is>
-      </c>
-      <c r="L29" s="37" t="inlineStr">
-        <is>
-          <t>DroneLife — Skyways Lands $37M Contract (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="M29" s="38" t="inlineStr">
-        <is>
-          <t>AP News — Skyways Secures $37M USAF Contract (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="N29" s="38" t="inlineStr">
-        <is>
-          <t>The Drone Girl — Skyways V3 Autonomous Cargo Drone (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="O29" s="38" t="inlineStr">
-        <is>
-          <t>UAS Weekly — Skyways Wins $37M USAF Contract (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="P29" s="38" t="inlineStr">
-        <is>
-          <t>Yahoo Finance — Skyways Secures $37M Contract (Jun 2025)</t>
-        </is>
-      </c>
+          <t>Charles Acknin Source Correction — $7M equity raise was separate from $5M Leonid debt. $7M was for STRATFI 1:1:2 matching; $5M Leonid was for cashflow management. Total: $12M</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
       <c r="Q29" s="28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R29" s="28" t="inlineStr">
@@ -2301,136 +2323,144 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="13">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>~$7M Private Capital Raise for STRATFI Match</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Skyways raised approximately $7M in private capital (including a $5M debt facility from defense-specialist lender Leonid Capital Partners) to meet the STRATFI 1:1:2 Government:SBIR:Private matching structure required for the $37M contract.</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Funding</t>
-        </is>
-      </c>
-      <c r="G30" s="37" t="inlineStr">
-        <is>
-          <t>Business Wire — $5M Debt Facility Announcement (Fact Error: Reported $5M debt facility only; total private raise was ~$7M for STRATFI 1:1:2 matching)</t>
-        </is>
-      </c>
-      <c r="H30" s="37" t="inlineStr">
-        <is>
-          <t>DroneLife — Skyways Secures $5M for Production (Jul 2025)</t>
-        </is>
-      </c>
-      <c r="I30" s="37" t="inlineStr">
-        <is>
-          <t>Skyways Newsroom</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Private raise was ~$7M total (not just $5M); needed for 1:1:2 Govt:SBIR:Private STRATFI matching structure</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="Q30" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R30" s="28" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Project ULTRA — 20 Operational Flights for DoD</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Defense Milestones</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Sole UAS provider for Project ULTRA, sponsored by OUSD (Office of the Under Secretary of Defense). At GrandSKY, ND: 10 round trips between Grand Forks AFB and Cavalier SFS over 12 days. All flights were BVLOS (Beyond Visual Line of Sight) in the National Airspace System (NAS). 230 lbs total cargo including temperature-controlled blood products at ~4°C. V3 Block 1 first customer flights. One unplanned emergency landing managed successfully.</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Defense — DoD</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>KX News — Project ULTRA expands, $100M ceiling (Jul 2025)</t>
+        </is>
+      </c>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>Air Cargo Week — Skyways completes historic flights (Aug 2025)</t>
+        </is>
+      </c>
+      <c r="I30" s="40" t="inlineStr">
+        <is>
+          <t>DroneLife — Skyways Historic Cargo Drone Flights (Aug 2025)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Sponsored by OUSD (not USD(A&amp;S)); flights were BVLOS in the NAS</t>
+        </is>
+      </c>
+      <c r="K30" s="40" t="inlineStr">
+        <is>
+          <t>Business Wire — Project ULTRA Press Release (Fact Error: Listed sponsor as USD(A&amp;S); correct sponsor is OUSD; did not specify flights were BVLOS in NAS)</t>
+        </is>
+      </c>
+      <c r="L30" s="40" t="inlineStr">
+        <is>
+          <t>Skyways Newsroom (Fact Error: Listed sponsor as USD(A&amp;S); correct sponsor is OUSD; did not specify flights were BVLOS in NAS)</t>
+        </is>
+      </c>
+      <c r="Q30" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R30" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="13">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Aug 2025</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Project ULTRA — 20 Operational Flights for DoD</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Defense Milestones</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Sole UAS provider for Project ULTRA, sponsored by OUSD (Office of the Under Secretary of Defense). At GrandSKY, ND: 10 round trips between Grand Forks AFB and Cavalier SFS over 12 days. All flights were BVLOS (Beyond Visual Line of Sight) in the National Airspace System (NAS). 230 lbs total cargo including temperature-controlled blood products at ~4°C. V3 Block 1 first customer flights. One unplanned emergency landing managed successfully.</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Defense — DoD</t>
-        </is>
-      </c>
-      <c r="G31" s="40" t="inlineStr">
-        <is>
-          <t>KX News — Project ULTRA expands, $100M ceiling (Jul 2025)</t>
-        </is>
-      </c>
-      <c r="H31" s="40" t="inlineStr">
-        <is>
-          <t>Air Cargo Week — Skyways completes historic flights (Aug 2025)</t>
-        </is>
-      </c>
-      <c r="I31" s="40" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>V3 Block 1 — First Customer Flights</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Product Development</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>V3 flies first customer missions during Project ULTRA at GrandSKY, ND. ~200 test flights completed including 8-hour endurance test. Block 1 is the test configuration preceding production-intent Block 2 and operational Block 2+ targeted for full-rate production by end of 2027.</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G31" s="39" t="inlineStr">
         <is>
           <t>DroneLife — Skyways Historic Cargo Drone Flights (Aug 2025)</t>
         </is>
       </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Sponsored by OUSD (not USD(A&amp;S)); flights were BVLOS in the NAS</t>
-        </is>
-      </c>
-      <c r="K31" s="40" t="inlineStr">
-        <is>
-          <t>Business Wire — Project ULTRA Press Release (Fact Error: Listed sponsor as USD(A&amp;S); correct sponsor is OUSD; did not specify flights were BVLOS in NAS)</t>
-        </is>
-      </c>
-      <c r="L31" s="40" t="inlineStr">
-        <is>
-          <t>Skyways Newsroom (Fact Error: Listed sponsor as USD(A&amp;S); correct sponsor is OUSD; did not specify flights were BVLOS in NAS)</t>
-        </is>
-      </c>
-      <c r="Q31" s="31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R31" s="31" t="inlineStr">
+      <c r="H31" s="39" t="inlineStr">
+        <is>
+          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="I31" s="39" t="inlineStr">
+        <is>
+          <t>Skyways Newsroom</t>
+        </is>
+      </c>
+      <c r="J31" s="38" t="inlineStr">
+        <is>
+          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="K31" s="39" t="inlineStr">
+        <is>
+          <t>The Drone Girl — From Cargo to Commuters Roadmap (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>The Drone Girl — From Cargo to Commuters Roadmap (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="Q31" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R31" s="30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2444,12 +2474,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>Sep 2025</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>V3 Block 1 — First Customer Flights</t>
+          <t>11 Consecutive Resupply Flights in One Day</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2459,7 +2489,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>V3 flies first customer missions during Project ULTRA at GrandSKY, ND. ~200 test flights completed including 8-hour endurance test. Block 1 is the test configuration preceding production-intent Block 2 and operational Block 2+ targeted for full-rate production by end of 2027.</t>
+          <t>V2 operational record: 11 flights, 9.4 hrs, 466 NM, zero human intervention, 8-min avg turnaround. $1K/hr vs $30K/hr for helicopter — a 30× cost reduction that represents the most compelling economic argument for autonomous cargo drones.</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -2469,34 +2499,21 @@
       </c>
       <c r="G32" s="39" t="inlineStr">
         <is>
-          <t>DroneLife — Skyways Historic Cargo Drone Flights (Aug 2025)</t>
+          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
         </is>
       </c>
       <c r="H32" s="39" t="inlineStr">
         <is>
-          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="I32" s="39" t="inlineStr">
-        <is>
-          <t>Skyways Newsroom</t>
-        </is>
-      </c>
-      <c r="J32" s="38" t="inlineStr">
-        <is>
           <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
         </is>
       </c>
-      <c r="K32" s="39" t="inlineStr">
-        <is>
-          <t>The Drone Girl — From Cargo to Commuters Roadmap (Dec 2025)</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>The Drone Girl — From Cargo to Commuters Roadmap (Dec 2025)</t>
-        </is>
-      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>KXAN Austin — Austin Aviation Company Scaling Drones (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
       <c r="Q32" s="30" t="inlineStr">
         <is>
           <t>No</t>
@@ -2509,127 +2526,136 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="13">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Sep 2025</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>11 Consecutive Resupply Flights in One Day</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Product Development</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>V2 operational record: 11 flights, 9.4 hrs, 466 NM, zero human intervention, 8-min avg turnaround. $1K/hr vs $30K/hr for helicopter — a 30× cost reduction that represents the most compelling economic argument for autonomous cargo drones.</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G33" s="39" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Feb–Apr 2025</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>First International Aircraft Deliveries</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>Major Milestones</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>Skyways begins delivering aircraft to commercial customers internationally for the first time. Skyports Drone Services takes delivery around February 2025, followed by ANA Holdings in approximately April 2025.</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="G33" s="38" t="inlineStr">
+        <is>
+          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
         </is>
       </c>
-      <c r="H33" s="39" t="inlineStr">
-        <is>
-          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>KXAN Austin — Austin Aviation Company Scaling Drones (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="Q33" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="I33" s="38" t="inlineStr">
+        <is>
+          <t>Energy Global — RWE pioneers cargo drone ops (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — First international aircraft deliveries: Skyports ~Feb 2025, ANA ~Apr 2025. Removed claim about 'transition from demo to customer operations' — U.S. Navy had been operating their own Skyways aircraft long before 2025</t>
+        </is>
+      </c>
+      <c r="K33" s="38" t="inlineStr">
+        <is>
+          <t>GlobeNewswire — Skyways Historic Cargo Deliveries</t>
+        </is>
+      </c>
+      <c r="L33" s="0" t="n"/>
+      <c r="Q33" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R33" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="13">
-      <c r="A34" s="0" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>Feb–Apr 2025</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>First International Aircraft Deliveries</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>Major Milestones</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>Skyways begins delivering aircraft to commercial customers internationally for the first time. Skyports Drone Services takes delivery around February 2025, followed by ANA Holdings in approximately April 2025. This marks the transition from demonstration flights to customers operating their own Skyways aircraft.</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="G34" s="38" t="inlineStr">
-        <is>
-          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="I34" s="38" t="inlineStr">
-        <is>
-          <t>Energy Global — RWE pioneers cargo drone ops (Oct 2025)</t>
-        </is>
-      </c>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — First international aircraft deliveries: Skyports ~Feb 2025, ANA ~Apr 2025</t>
-        </is>
-      </c>
-      <c r="K34" s="38" t="inlineStr">
-        <is>
-          <t>GlobeNewswire — Skyways Historic Cargo Deliveries</t>
-        </is>
-      </c>
-      <c r="L34" s="0" t="n"/>
-      <c r="Q34" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R34" s="32" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Sep–Oct 2025</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>RWE Offshore Wind Farm — Baltic Sea, Germany</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Contracts &amp; Funding</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Germany's first long-range BVLOS offshore wind drone delivery. Partnered with RWE and Skyports Drone Services. V2 flew 50-mi round trips from Mukran Port to Arkona Wind Farm, delivering up to 22 lbs to turbine nacelles in 29.7-knot winds. Delivery: 26 min vs 2+ hrs by vessel. RWE plans to scale across global wind portfolio.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Contract — RWE (Germany)</t>
+        </is>
+      </c>
+      <c r="G34" s="37" t="inlineStr">
+        <is>
+          <t>RWE — Pioneers cargo drone operations (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="H34" s="37" t="inlineStr">
+        <is>
+          <t>Unmanned Systems Technology — Autonomous Cargo Drone (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="I34" s="37" t="inlineStr">
+        <is>
+          <t>eVTOL Insights — Germany first long-range deliveries (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>DroneXL — Skyways Drone Cuts Supply Time (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="K34" s="37" t="inlineStr">
+        <is>
+          <t>DroneLife — Germany First Long-Range Deliveries (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="n"/>
+      <c r="Q34" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R34" s="28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2643,12 +2669,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Sep–Oct 2025</t>
+          <t>Oct 2025</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>RWE Offshore Wind Farm — Baltic Sea, Germany</t>
+          <t>ANA Holdings Partnership &amp; $1M Investment</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2658,40 +2684,44 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Germany's first long-range BVLOS offshore wind drone delivery. Partnered with RWE and Skyports Drone Services. V2 flew 50-mi round trips from Mukran Port to Arkona Wind Farm, delivering up to 22 lbs to turbine nacelles in 29.7-knot winds. Delivery: 26 min vs 2+ hrs by vessel. RWE plans to scale across global wind portfolio.</t>
+          <t>ANA Holdings invested $1M, signed long-term partnership. Drones fly between Okinawan islands carrying pharmaceuticals and blood samples under Japan MLIT oversight. Routes: 89–100 km with temperature-controlled boxes. ANA targets commercial drone delivery across APAC by FY2027–2029 with dedicated Skyways pilot training program. NOTE: Coordinate messaging with Jessica Hogan — ANA has been cautious about public disclosure due to Skyways' DoD ties.</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Contract — RWE (Germany)</t>
+          <t>Contract — ANA Holdings (Japan)</t>
         </is>
       </c>
       <c r="G35" s="37" t="inlineStr">
         <is>
-          <t>RWE — Pioneers cargo drone operations (Oct 2025)</t>
+          <t>Yomiuri Shimbun — ANA builds drone logistics network (Jan 2026)</t>
         </is>
       </c>
       <c r="H35" s="37" t="inlineStr">
         <is>
-          <t>Unmanned Systems Technology — Autonomous Cargo Drone (Oct 2025)</t>
+          <t>Japan Today / Kyodo — ANA drone delivery by FY2028</t>
         </is>
       </c>
       <c r="I35" s="37" t="inlineStr">
         <is>
-          <t>eVTOL Insights — Germany first long-range deliveries (Oct 2025)</t>
-        </is>
-      </c>
-      <c r="J35" s="38" t="inlineStr">
-        <is>
-          <t>DroneXL — Skyways Drone Cuts Supply Time (Oct 2025)</t>
+          <t>Payload Asia — ANA Okinawa medical drone trials (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Coordinate messaging with Jessica Hogan; ANA cautious about public disclosure due to DoD ties</t>
         </is>
       </c>
       <c r="K35" s="37" t="inlineStr">
         <is>
-          <t>DroneLife — Germany First Long-Range Deliveries (Oct 2025)</t>
-        </is>
-      </c>
-      <c r="L35" s="16" t="n"/>
+          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>The Drone Girl — From cargo to commuters (Dec 2025)</t>
+        </is>
+      </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
           <t>No</t>
@@ -2704,72 +2734,59 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="13">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>ANA Holdings Partnership &amp; $1M Investment</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Contracts &amp; Funding</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ANA Holdings invested $1M, signed long-term partnership. Drones fly between Okinawan islands carrying pharmaceuticals and blood samples under Japan MLIT oversight. Routes: 89–100 km with temperature-controlled boxes. ANA targets commercial drone delivery across APAC by FY2027–2029 with dedicated Skyways pilot training program. NOTE: Coordinate messaging with Jessica Hogan — ANA has been cautious about public disclosure due to Skyways' DoD ties.</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Contract — ANA Holdings (Japan)</t>
-        </is>
-      </c>
-      <c r="G36" s="37" t="inlineStr">
-        <is>
-          <t>Yomiuri Shimbun — ANA builds drone logistics network (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="H36" s="37" t="inlineStr">
-        <is>
-          <t>Japan Today / Kyodo — ANA drone delivery by FY2028</t>
-        </is>
-      </c>
-      <c r="I36" s="37" t="inlineStr">
-        <is>
-          <t>Payload Asia — ANA Okinawa medical drone trials (Mar 2026)</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Coordinate messaging with Jessica Hogan; ANA cautious about public disclosure due to DoD ties</t>
-        </is>
-      </c>
-      <c r="K36" s="37" t="inlineStr">
-        <is>
-          <t>The Drone Girl — Inside Skyways (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="L36" s="37" t="inlineStr">
-        <is>
-          <t>The Drone Girl — From cargo to commuters (Dec 2025)</t>
-        </is>
-      </c>
-      <c r="Q36" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R36" s="28" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Nov–Dec 2025</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Stealth Exit — Public Emergence</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Major Milestones</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>First-ever press Demo Day near Austin. Journalist Sally French of The Drone Girl watched V2 and V3 fly from a 'cow-dotted field' beside a converted trailer hangar. Her two-part feature became the definitive company profile. After 8 years of near-total obscurity, Skyways entered the public conversation. Coverage remains concentrated in drone trade media; mainstream tech, defense, and business press largely unaware.</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="G36" s="41" t="inlineStr">
+        <is>
+          <t>The Drone Girl — Inside Skyways aspirations (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="H36" s="41" t="inlineStr">
+        <is>
+          <t>The Drone Girl — From cargo to commuters roadmap (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I36" s="41" t="inlineStr">
+        <is>
+          <t>KXAN Austin/NBC — Austin aviation company scaling drones (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="Q36" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R36" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2778,17 +2795,17 @@
     <row r="37" ht="15.75" customHeight="1" s="13">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Nov–Dec 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Stealth Exit — Public Emergence</t>
+          <t>Leadership Team Expansion</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2798,7 +2815,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>First-ever press Demo Day near Austin. Journalist Sally French of The Drone Girl watched V2 and V3 fly from a 'cow-dotted field' beside a converted trailer hangar. Her two-part feature became the definitive company profile. After 8 years of near-total obscurity, Skyways entered the public conversation. Coverage remains concentrated in drone trade media; mainstream tech, defense, and business press largely unaware.</t>
+          <t>Key hires: Jeff Weinstein (VP Production), Bill Wimberley (CCO), Gabrielle Wain (VP Regulatory, ex-Zipline/Iris Automation), Mike Uffelman (Head of Flight Ops, ex-USAF, 2,500+ mil flight hrs). Company finished 2025 at approximately 39 employees (verify with Anthony). Plans to double headcount in 2026.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2808,24 +2825,29 @@
       </c>
       <c r="G37" s="41" t="inlineStr">
         <is>
-          <t>The Drone Girl — Inside Skyways aspirations (Nov 2025)</t>
+          <t>Austin American-Statesman — In-depth Skyways profile (Feb 2026) (Fact Error: Reported approximately 30 employees; company finished 2025 at ~39 employees per Charles)</t>
         </is>
       </c>
       <c r="H37" s="41" t="inlineStr">
         <is>
-          <t>The Drone Girl — From cargo to commuters roadmap (Dec 2025)</t>
+          <t>DroneXL — Skyways Plans Worlds Largest Fleet (Feb 2026)</t>
         </is>
       </c>
       <c r="I37" s="41" t="inlineStr">
         <is>
-          <t>KXAN Austin/NBC — Austin aviation company scaling drones (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
+          <t>GlobeNewswire — Skyways Strengthens Leadership (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>Charles Acknin Source Correction — Company finished 2025 at ~39 employees (verify with Anthony)</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
       <c r="Q37" s="26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R37" s="26" t="inlineStr">
@@ -2842,12 +2864,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Leadership Team Expansion</t>
+          <t>ANA Completes Okinawa Medical Delivery Trials</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2857,7 +2879,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Key hires: Jeff Weinstein (VP Production), Bill Wimberley (CCO), Gabrielle Wain (VP Regulatory, ex-Zipline/Iris Automation), Mike Uffelman (Head of Flight Ops, ex-USAF, 2,500+ mil flight hrs). Company finished 2025 at approximately 39 employees (verify with Anthony). Plans to double headcount in 2026.</t>
+          <t>Long-distance pharmaceutical and blood sample deliveries across Okinawa Prefecture under Japan MLIT. ANA targets commercial drone delivery across APAC by FY2027–2029, a significant international commercial growth vector. Developing dedicated Skyways pilot training program.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2867,26 +2889,17 @@
       </c>
       <c r="G38" s="41" t="inlineStr">
         <is>
-          <t>Austin American-Statesman — In-depth Skyways profile (Feb 2026) (Fact Error: Reported approximately 30 employees; company finished 2025 at ~39 employees per Charles)</t>
+          <t>Payload Asia — ANA completes Okinawa trials (Mar 2026)</t>
         </is>
       </c>
       <c r="H38" s="41" t="inlineStr">
         <is>
-          <t>DroneXL — Skyways Plans Worlds Largest Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="I38" s="41" t="inlineStr">
-        <is>
-          <t>GlobeNewswire — Skyways Strengthens Leadership (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>Charles Acknin Source Correction — Company finished 2025 at ~39 employees (verify with Anthony)</t>
-        </is>
-      </c>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
+          <t>Japan Today — ANA drone delivery by FY2028</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
       <c r="Q38" s="26" t="inlineStr">
         <is>
           <t>No</t>
@@ -2899,74 +2912,74 @@
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="13">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>ANA Completes Okinawa Medical Delivery Trials</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Major Milestones</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Long-distance pharmaceutical and blood sample deliveries across Okinawa Prefecture under Japan MLIT. ANA targets commercial drone delivery across APAC by FY2027–2029, a significant international commercial growth vector. Developing dedicated Skyways pilot training program.</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="G39" s="41" t="inlineStr">
-        <is>
-          <t>Payload Asia — ANA completes Okinawa trials (Mar 2026)</t>
-        </is>
-      </c>
-      <c r="H39" s="41" t="inlineStr">
-        <is>
-          <t>Japan Today — ANA drone delivery by FY2028</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-      <c r="Q39" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R39" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>H2 2026</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>V3 Production Ramp Begins</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Product Development</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>V3 Block 2 (production-intent) expected in service H2 2026. Program of Record designation in progress. Scaling from ~39 employees to full-rate manufacturing is the fundamental execution challenge. Hybrid VTOL drone market projected to grow from $1.34B (2024) to $14.4B by 2034.</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="G39" s="39" t="inlineStr">
+        <is>
+          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="H39" s="39" t="inlineStr">
+        <is>
+          <t>ADrones — Skyways Plans Largest Fleet (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="Q39" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R39" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="13">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>H2 2026</t>
+          <t>End of 2027</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>V3 Production Ramp Begins</t>
+          <t>V3 Full-Rate Production Target</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2976,7 +2989,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>V3 Block 2 (production-intent) expected in service H2 2026. Program of Record designation in progress. Scaling from ~39 employees to full-rate manufacturing is the fundamental execution challenge. Hybrid VTOL drone market projected to grow from $1.34B (2024) to $14.4B by 2034.</t>
+          <t>Full-rate V3 production targeted with Program of Record designation complete. Pentagon FY2026 budget: $9.4B for aerial drones, $13.4B for AI/autonomous systems. Defense-tech VC hit record $49.1B in 2025. Success depends on production execution, Chinese supply chain decoupling (battery cells), and sustained procurement momentum.</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3008,61 +3021,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="13">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>End of 2027</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>V3 Full-Rate Production Target</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Product Development</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Full-rate V3 production targeted with Program of Record designation complete. Pentagon FY2026 budget: $9.4B for aerial drones, $13.4B for AI/autonomous systems. Defense-tech VC hit record $49.1B in 2025. Success depends on production execution, Chinese supply chain decoupling (battery cells), and sustained procurement momentum.</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="G41" s="39" t="inlineStr">
-        <is>
-          <t>DroneXL — Skyways Autonomous Drone Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="H41" s="39" t="inlineStr">
-        <is>
-          <t>ADrones — Skyways Plans Largest Fleet (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-      <c r="L41" s="8" t="n"/>
-      <c r="Q41" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R41" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
+    <row r="41" ht="15.75" customHeight="1" s="13"/>
     <row r="42" ht="15.75" customHeight="1" s="13"/>
     <row r="43" ht="15.75" customHeight="1" s="13"/>
     <row r="44" ht="15.75" customHeight="1" s="13"/>
@@ -4058,84 +4017,82 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
